--- a/outils/Cahier_de_recette_evolution5.xlsx
+++ b/outils/Cahier_de_recette_evolution5.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cahier de recette'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cahier de recette'!$A$1:$G$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cahier de recette'!$A$1:$G$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.5" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F3" s="6">
-        <f>COUNTA(E10:E121)</f>
+        <f>COUNTA(E10:E131)</f>
         <v/>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="F4" s="6">
-        <f>COUNTIF(F10:F121,"OK")</f>
+        <f>COUNTIF(F10:F131,"OK")</f>
         <v/>
       </c>
       <c r="G4" s="8" t="n"/>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIF(F10:F121,"KO")</f>
+        <f>COUNTIF(F10:F131,"KO")</f>
         <v/>
       </c>
       <c r="G5" s="8" t="n"/>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIF(F10:F121,"N/A")</f>
+        <f>COUNTIF(F10:F131,"N/A")</f>
         <v/>
       </c>
       <c r="G6" s="8" t="n"/>
@@ -908,7 +908,7 @@
       <c r="F17" s="15" t="n"/>
       <c r="G17" s="16" t="n"/>
     </row>
-    <row r="18" ht="54" customHeight="1">
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>B2</t>
@@ -916,22 +916,22 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Couleurs</t>
+          <t>Couleurs des onglets</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Regarder les quatre onglets.</t>
+          <t>Regarder les quatre onglets, puis passer d'un onglet à l'autre.</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Chaque onglet porte sa couleur : vert (saisie de vente), bleu (valorisation), orange (chiffre d'affaires), violet (point de caisse). L'onglet actif a un fond teinté et son libellé en gras.</t>
+          <t>C'est le FOND de l'onglet qui est coloré, pas son texte : vert (saisie de vente), bleu (valorisation), orange (chiffre d'affaires), violet (point de caisse). Le libellé reste blanc sur les quatre. L'onglet ouvert porte la teinte pleine, les autres la même teinte en clair : on lit d'un coup d'œil où l'on est.</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>d1ec13e</t>
+          <t>893f936</t>
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
@@ -1298,7 +1298,7 @@
       <c r="F31" s="15" t="n"/>
       <c r="G31" s="16" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="54" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>C8</t>
@@ -1306,22 +1306,22 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Filtre sur le stock</t>
+          <t>Filtre sur le stock : opérateur et valeur</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Choisir successivement Négatif, À zéro, Positif dans le filtre Stock.</t>
+          <t>Dans le filtre Stock, choisir un opérateur (=, &lt;&gt;, &lt;, &lt;=, &gt;, &gt;=) puis saisir une valeur et valider par Entrée. Essayer « &lt; 0 », « = 0 », « &gt; 0 », « &gt;= 10 ».</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Chaque choix ne garde que les lignes correspondantes. Le nombre total et la valorisation suivent à chaque fois.</t>
+          <t>Chaque couple ne garde que les lignes correspondantes ; le nombre total et la valorisation suivent. La zone de valeur reste GRISÉE tant qu'aucun opérateur n'est choisi, et accepte les valeurs négatives.</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>893f936</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
@@ -1330,27 +1330,27 @@
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C8b</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Pas de critère contradictoire</t>
+          <t>Filtre de stock rappelé à l'impression</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Choisir un filtre Stock autre que « Tous ».</t>
+          <t>Poser « stock &gt;= 10 », puis Imprimer.</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>La case « masquer les articles à 0 » devient GRISÉE : le filtre décide. Revenir à « Tous » la rend de nouveau utilisable.</t>
+          <t>Le rappel de critères du PDF nomme le filtre tel qu'il a été posé : « stock &gt;= 10 ». Une édition qui tait son filtre laisse croire qu'elle porte sur tout le dépôt.</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>893f936</t>
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
@@ -1359,56 +1359,56 @@
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Filtre emplacement</t>
+          <t>Pas de critère contradictoire</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>Choisir un rayon dans le filtre Emplacement (à côté du filtre Famille).</t>
+          <t>Poser un opérateur dans le filtre Stock.</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Seuls les articles de ce RAYON restent. Attention : c'est bien le rayon de l'article, le dépôt étant déjà choisi en haut.</t>
+          <t>La case « masquer les articles à 0 » devient GRISÉE : le filtre décide. Revenir à « Tous » la rend de nouveau utilisable, et regrise la zone de valeur.</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>893f936</t>
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
       <c r="G34" s="16" t="n"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="42" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Recherche</t>
+          <t>Filtre emplacement</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Saisir un CIP ou un début de désignation, puis Entrée ou Rechercher.</t>
+          <t>Choisir un rayon dans le filtre Emplacement (à côté du filtre Famille).</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Seuls les articles correspondants restent, et la valorisation ne porte plus que sur eux.</t>
+          <t>Seuls les articles de ce RAYON restent. Attention : c'est bien le rayon de l'article, le dépôt étant déjà choisi en haut.</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>adc587e</t>
+          <t>28b590f</t>
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
@@ -1417,22 +1417,22 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Export Excel</t>
+          <t>Recherche</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Exporter Excel ».</t>
+          <t>Saisir un CIP ou un début de désignation, puis Entrée ou Rechercher.</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Le fichier se télécharge, nommé d'après le dépôt (stock_depot_&lt;DEPOT&gt;.xls), et porte les critères appliqués.</t>
+          <t>Seuls les articles correspondants restent, et la valorisation ne porte plus que sur eux.</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -1443,25 +1443,25 @@
       <c r="F36" s="15" t="n"/>
       <c r="G36" s="16" t="n"/>
     </row>
-    <row r="37" ht="54" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Édition PDF</t>
+          <t>Export Excel</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Imprimer » depuis la liste des articles.</t>
+          <t>Cliquer « Exporter Excel ».</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Le PDF s'ouvre DANS un onglet du navigateur (aucune fenêtre surgissante, aucun téléchargement). Il nomme le dépôt, rappelle les critères avec les mots de l'écran, et porte les colonnes de stock et de valorisation.</t>
+          <t>Le fichier se télécharge, nommé d'après le dépôt (stock_depot_&lt;DEPOT&gt;.xls), et porte les critères appliqués.</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -1472,159 +1472,159 @@
       <c r="F37" s="15" t="n"/>
       <c r="G37" s="16" t="n"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="54" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Pagination du PDF</t>
+          <t>Édition PDF</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Faire défiler le PDF jusqu'à la dernière page.</t>
+          <t>Cliquer « Imprimer » depuis la liste des articles.</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Chaque page porte « Page X / Y », la date, l'opérateur, et le rappel que la liste est triée par emplacement.</t>
+          <t>Le PDF s'ouvre DANS un onglet du navigateur (aucune fenêtre surgissante, aucun téléchargement). Il nomme le dépôt, rappelle les critères avec les mots de l'écran, et porte les colonnes de stock et de valorisation.</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>adc587e</t>
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
       <c r="G38" s="16" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Pagination du PDF</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Faire défiler le PDF jusqu'à la dernière page.</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Chaque page porte « Page X / Y », la date, l'opérateur, et le rappel que la liste est triée par emplacement.</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>28b590f</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>D. ONGLET VALORISATION — PAR EMPLACEMENT</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-    </row>
-    <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Ventilation</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>Cliquer « Valorisation par emplacement ».</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Une ligne par rayon, avec RÉFÉRENCES, UNITÉS, valeur d'achat et valeur de vente. Les articles sans rayon sont regroupés sous « Sans emplacement » — leur valeur n'est pas perdue.</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>647702e</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="16" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
     </row>
     <row r="41" ht="54" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Deux grandeurs distinctes</t>
+          <t>Ventilation</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Survoler les en-têtes RÉFÉRENCES et UNITÉS.</t>
+          <t>Cliquer « Valorisation par emplacement ».</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Les infobulles disent la différence : RÉFÉRENCES compte les articles différents du rayon, UNITÉS additionne les quantités. C'était la question posée sur l'ancienne colonne « quantité ».</t>
+          <t>Une ligne par rayon, avec RÉFÉRENCES, UNITÉS, valeur d'achat et valeur de vente. Les articles sans rayon sont regroupés sous « Sans emplacement » — leur valeur n'est pas perdue.</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>647702e</t>
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
       <c r="G41" s="16" t="n"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="54" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Somme = total</t>
+          <t>Deux grandeurs distinctes</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>Additionner à la main les valeurs d'achat des lignes et comparer au total rappelé en bas.</t>
+          <t>Survoler les en-têtes RÉFÉRENCES et UNITÉS.</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>La somme des lignes fait EXACTEMENT le total du dépôt.</t>
+          <t>Les infobulles disent la différence : RÉFÉRENCES compte les articles différents du rayon, UNITÉS additionne les quantités. C'était la question posée sur l'ancienne colonne « quantité ».</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>647702e</t>
+          <t>28b590f</t>
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
       <c r="G42" s="16" t="n"/>
     </row>
-    <row r="43" ht="42" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Critères partagés (aller)</t>
+          <t>Somme = total</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Dans « Liste des articles », chercher un produit présent dans un seul rayon. Puis cliquer « Valorisation par emplacement ».</t>
+          <t>Additionner à la main les valeurs d'achat des lignes et comparer au total rappelé en bas.</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Seul ce rayon apparaît : la recherche faite dans une vue vaut pour l'autre.</t>
+          <t>La somme des lignes fait EXACTEMENT le total du dépôt.</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>647702e</t>
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
@@ -1633,22 +1633,22 @@
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Critères partagés (retour)</t>
+          <t>Critères partagés (aller)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Depuis la vue par emplacement, effacer la recherche et relancer.</t>
+          <t>Dans « Liste des articles », chercher un produit présent dans un seul rayon. Puis cliquer « Valorisation par emplacement ».</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>La vue par emplacement se met à jour immédiatement et remontre tous les rayons. Les critères restent visibles et modifiables dans les DEUX vues.</t>
+          <t>Seul ce rayon apparaît : la recherche faite dans une vue vaut pour l'autre.</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
@@ -1659,25 +1659,25 @@
       <c r="F44" s="15" t="n"/>
       <c r="G44" s="16" t="n"/>
     </row>
-    <row r="45" ht="54" customHeight="1">
+    <row r="45" ht="42" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Impression</t>
+          <t>Critères partagés (retour)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Imprimer » alors que la vue par emplacement est affichée.</t>
+          <t>Depuis la vue par emplacement, effacer la recherche et relancer.</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>C'est l'édition PAR EMPLACEMENT qui sort (titre « VALORISATION PAR EMPLACEMENT - &lt;dépôt&gt; »), avec les colonnes RÉFÉRENCES et UNITÉS, sa ligne TOTAL, et sa pagination. Le même bouton édite donc ce qui est affiché.</t>
+          <t>La vue par emplacement se met à jour immédiatement et remontre tous les rayons. Les critères restent visibles et modifiables dans les DEUX vues.</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -1688,25 +1688,25 @@
       <c r="F45" s="15" t="n"/>
       <c r="G45" s="16" t="n"/>
     </row>
-    <row r="46" ht="42" customHeight="1">
+    <row r="46" ht="54" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Export Excel</t>
+          <t>Impression</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>Regarder le bouton « Exporter Excel » dans la vue par emplacement.</t>
+          <t>Cliquer « Imprimer » alors que la vue par emplacement est affichée.</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Il est mis en retrait : l'export ne vaut que pour la liste des articles. Il redevient actif en revenant sur celle-ci.</t>
+          <t>C'est l'édition PAR EMPLACEMENT qui sort (titre « VALORISATION PAR EMPLACEMENT - &lt;dépôt&gt; »), avec les colonnes RÉFÉRENCES et UNITÉS, sa ligne TOTAL, et sa pagination. Le même bouton édite donc ce qui est affiché.</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -1717,72 +1717,72 @@
       <c r="F46" s="15" t="n"/>
       <c r="G46" s="16" t="n"/>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Export Excel</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Regarder le bouton « Exporter Excel » dans la vue par emplacement.</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Il est mis en retrait : l'export ne vaut que pour la liste des articles. Il redevient actif en revenant sur celle-ci.</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>28b590f</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>E. ONGLET SAISIR VENTE DÉPÔT</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Un seul endroit</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>Chercher dans les menus un menu séparé « Vente du dépôt ».</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>Il n'existe plus : la saisie de vente en dépôt vit uniquement dans cet onglet.</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>V6.9.48</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="16" t="n"/>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>Écran complet</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>Ouvrir l'onglet et parcourir l'écran.</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>C'est l'écran de vente complet : type de vente, tiers payants, remises, avoirs, préventes, règlements. L'écran de vente de l'officine n'est pas touché.</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>4a5bb90</t>
         </is>
       </c>
       <c r="F49" s="15" t="n"/>
@@ -1791,27 +1791,27 @@
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Dépôt imposé</t>
+          <t>Écran complet</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Regarder le champ « Dépôt » dans l'onglet de vente.</t>
+          <t>Ouvrir l'onglet et parcourir l'écran.</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Il reprend le dépôt choisi en haut de l'écran, en LECTURE SEULE et grisé, mais lisible. Il n'est jamais encadré de rouge : ce n'est plus une saisie, c'est un rappel.</t>
+          <t>C'est l'écran de vente complet : type de vente, tiers payants, remises, avoirs, préventes, règlements. L'écran de vente de l'officine n'est pas touché.</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>647702e</t>
+          <t>4a5bb90</t>
         </is>
       </c>
       <c r="F50" s="15" t="n"/>
@@ -1820,22 +1820,22 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Titre</t>
+          <t>Dépôt imposé</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>Lire le titre de l'écran de vente.</t>
+          <t>Regarder le champ « Dépôt » dans l'onglet de vente.</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Il nomme le dépôt en cours. Si aucun dépôt n'est choisi en haut, le titre n'en nomme AUCUN : il ne garde jamais le nom d'un dépôt précédent.</t>
+          <t>Il reprend le dépôt choisi en haut de l'écran, en LECTURE SEULE et grisé, mais lisible. Il n'est jamais encadré de rouge : ce n'est plus une saisie, c'est un rappel.</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -1849,56 +1849,56 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Après une vente validée</t>
+          <t>Titre</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>Saisir et valider une vente dans le dépôt.</t>
+          <t>Lire le titre de l'écran de vente.</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Le dépôt en cours est CONSERVÉ et reste grisé : il ne disparaît pas, et n'apparaît pas en rouge. Le titre continue de le nommer.</t>
+          <t>Il nomme le dépôt en cours. Si aucun dépôt n'est choisi en haut, le titre n'en nomme AUCUN : il ne garde jamais le nom d'un dépôt précédent.</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>bc094f1</t>
+          <t>647702e</t>
         </is>
       </c>
       <c r="F52" s="15" t="n"/>
       <c r="G52" s="16" t="n"/>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="42" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Stock du dépôt</t>
+          <t>Après une vente validée</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>Vendre un article, puis vérifier le stock de cet article dans l'onglet Valorisation.</t>
+          <t>Saisir et valider une vente dans le dépôt.</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>C'est le stock du DÉPÔT qui a baissé, pas celui de l'officine.</t>
+          <t>Le dépôt en cours est CONSERVÉ et reste grisé : il ne disparaît pas, et n'apparaît pas en rouge. Le titre continue de le nommer.</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>82c3055</t>
+          <t>bc094f1</t>
         </is>
       </c>
       <c r="F53" s="15" t="n"/>
@@ -1907,22 +1907,22 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>On ne vend que ce que le dépôt détient</t>
+          <t>Stock du dépôt</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>Tenter de vendre un article que le dépôt ne détient pas.</t>
+          <t>Vendre un article, puis vérifier le stock de cet article dans l'onglet Valorisation.</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>La vente est refusée : le dépôt ne peut pas vendre un article qu'il n'a pas.</t>
+          <t>C'est le stock du DÉPÔT qui a baissé, pas celui de l'officine.</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
@@ -1933,125 +1933,125 @@
       <c r="F54" s="15" t="n"/>
       <c r="G54" s="16" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Où va l'argent</t>
+          <t>On ne vend que ce que le dépôt détient</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>Valider une vente en dépôt, puis regarder la caisse de l'opérateur connecté.</t>
+          <t>Tenter de vendre un article que le dépôt ne détient pas.</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>L'argent est dans la caisse de l'OPÉRATEUR de l'officine : le chiffre appartient au dépôt, l'encaissement à l'officine.</t>
+          <t>La vente est refusée : le dépôt ne peut pas vendre un article qu'il n'a pas.</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>52da772</t>
+          <t>82c3055</t>
         </is>
       </c>
       <c r="F55" s="15" t="n"/>
       <c r="G55" s="16" t="n"/>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56" ht="42" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Non-régression officine</t>
+          <t>Où va l'argent</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir l'écran de vente habituel de l'officine et enchaîner une vente ordinaire.</t>
+          <t>Valider une vente en dépôt, puis regarder la caisse de l'opérateur connecté.</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Rien n'a changé : même écran, même comportement, même stock de l'officine mouvementé.</t>
+          <t>L'argent est dans la caisse de l'OPÉRATEUR de l'officine : le chiffre appartient au dépôt, l'encaissement à l'officine.</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>82c3055</t>
+          <t>52da772</t>
         </is>
       </c>
       <c r="F56" s="15" t="n"/>
       <c r="G56" s="16" t="n"/>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Non-régression officine</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir l'écran de vente habituel de l'officine et enchaîner une vente ordinaire.</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Rien n'a changé : même écran, même comportement, même stock de l'officine mouvementé.</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>82c3055</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="n"/>
+      <c r="G57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>F. ONGLET CHIFFRE D'AFFAIRES DU DÉPÔT</t>
         </is>
       </c>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>Dates du jour</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Ouvrir l'onglet Chiffre d'affaires.</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>La période part des dates DU JOUR (du jour au jour). Rien n'est chargé tant que la recherche n'est pas lancée, et le bouton Imprimer est inactif.</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>1ef2bce</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="16" t="n"/>
-    </row>
-    <row r="59" ht="54" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>Colonnes demandées</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>Lancer une recherche et parcourir les colonnes.</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Dans cet ordre : TYPE DE VENTE, MONTANT TTC, MONTANT NET, MARGE, NBRE VENTES, MONTANT ESPÈCES, MONTANT TIERS PAYANT. La colonne « règlement » a disparu (elle n'était jamais renseignée).</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
@@ -2062,25 +2062,25 @@
       <c r="F59" s="15" t="n"/>
       <c r="G59" s="16" t="n"/>
     </row>
-    <row r="60" ht="42" customHeight="1">
+    <row r="60" ht="54" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Ligne TOTAL</t>
+          <t>Colonnes demandées</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>Regarder sous les lignes.</t>
+          <t>Lancer une recherche et parcourir les colonnes.</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Une ligne TOTAL additionne chaque colonne de montant. Vérifier à la main que le total du net est bien la somme des lignes.</t>
+          <t>Dans cet ordre : TYPE DE VENTE, MONTANT TTC, MONTANT NET, MARGE, NBRE VENTES, MONTANT ESPÈCES, MONTANT TIERS PAYANT. La colonne « règlement » a disparu (elle n'était jamais renseignée).</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -2094,27 +2094,27 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Le CA appartient au dépôt</t>
+          <t>Ligne TOTAL</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>Jouer une vente dans le dépôt, puis comparer le CA du dépôt et le CA de l'officine sur le même jour.</t>
+          <t>Regarder sous les lignes.</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Le CA du dépôt compte cette vente ; le CA de l'officine ne la compte PAS. Une vente d'officine ordinaire fait l'inverse. Les deux ne se recouvrent jamais.</t>
+          <t>Une ligne TOTAL additionne chaque colonne de montant. Vérifier à la main que le total du net est bien la somme des lignes.</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>52da772</t>
+          <t>1ef2bce</t>
         </is>
       </c>
       <c r="F61" s="15" t="n"/>
@@ -2123,80 +2123,80 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Temps de réponse</t>
+          <t>Le CA appartient au dépôt</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>Lancer la recherche sur un jour, puis sur un mois, puis sur un an.</t>
+          <t>Jouer une vente dans le dépôt, puis comparer le CA du dépôt et le CA de l'officine sur le même jour.</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>La réponse est immédiate (mesure au banc : 13 à 16 ms). Les 6,85 s signalées le 17/09 étaient une régression, corrigée.</t>
+          <t>Le CA du dépôt compte cette vente ; le CA de l'officine ne la compte PAS. Une vente d'officine ordinaire fait l'inverse. Les deux ne se recouvrent jamais.</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>28b590f</t>
+          <t>52da772</t>
         </is>
       </c>
       <c r="F62" s="15" t="n"/>
       <c r="G62" s="16" t="n"/>
     </row>
-    <row r="63" ht="54" customHeight="1">
+    <row r="63" ht="42" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Impression</t>
+          <t>Temps de réponse</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Imprimer » après une recherche.</t>
+          <t>Lancer la recherche sur un jour, puis sur un mois, puis sur un an.</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Le PDF s'ouvre dans un onglet. Mêmes colonnes que l'écran, ligne TOTAL, pagination, rappel de la période, et le rappel imprimé que l'argent est dans la caisse de l'opérateur. Les chiffres du PDF sont ceux de l'écran.</t>
+          <t>La réponse est immédiate (mesure au banc : 13 à 16 ms). Les 6,85 s signalées le 17/09 étaient une régression, corrigée.</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>1ef2bce</t>
+          <t>28b590f</t>
         </is>
       </c>
       <c r="F63" s="15" t="n"/>
       <c r="G63" s="16" t="n"/>
     </row>
-    <row r="64" ht="42" customHeight="1">
+    <row r="64" ht="54" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Période sans vente</t>
+          <t>Impression</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>Imprimer sur une période où le dépôt n'a rien vendu.</t>
+          <t>Cliquer « Imprimer » après une recherche.</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Le document le DIT (« Ce dépôt n'a enregistré aucune vente sur la période demandée ») au lieu de rendre une page vide.</t>
+          <t>Le PDF s'ouvre dans un onglet. Mêmes colonnes que l'écran, ligne TOTAL, pagination, rappel de la période, et le rappel imprimé que l'argent est dans la caisse de l'opérateur. Les chiffres du PDF sont ceux de l'écran.</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -2207,67 +2207,67 @@
       <c r="F64" s="15" t="n"/>
       <c r="G64" s="16" t="n"/>
     </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Période sans vente</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Imprimer sur une période où le dépôt n'a rien vendu.</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Le document le DIT (« Ce dépôt n'a enregistré aucune vente sur la période demandée ») au lieu de rendre une page vide.</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>1ef2bce</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="n"/>
+      <c r="G65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>G. ONGLET POINT DE CAISSE</t>
         </is>
       </c>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
-    </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>Écran embarqué</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>Ouvrir l'onglet Point de caisse.</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>C'est l'écran « Point Caisse Dépôt » existant, avec ses colonnes (Date/Période, Dépôt, Caissière, Montant Net, Espèces, Crédit) et son total.</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>d1ec13e</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="n"/>
-      <c r="G66" s="16" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Même dépôt que les voisins</t>
+          <t>Écran embarqué</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>Choisir un dépôt en haut de l'écran, puis venir sur l'onglet Point de caisse.</t>
+          <t>Ouvrir l'onglet Point de caisse.</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Le dépôt choisi lui est IMPOSÉ et la recherche est relancée : les quatre onglets parlent du même dépôt. Le choix reste modifiable dans l'onglet.</t>
+          <t>C'est l'écran « Point Caisse Dépôt » existant, avec ses colonnes (Date/Période, Dépôt, Caissière, Montant Net, Espèces, Crédit) et son total.</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -2278,25 +2278,25 @@
       <c r="F67" s="15" t="n"/>
       <c r="G67" s="16" t="n"/>
     </row>
-    <row r="68" ht="30" customHeight="1">
+    <row r="68" ht="42" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>Menu d'origine conservé</t>
+          <t>Même dépôt que les voisins</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir le menu « Point Caisse Dépôt » habituel.</t>
+          <t>Choisir un dépôt en haut de l'écran, puis venir sur l'onglet Point de caisse.</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Il fonctionne exactement comme avant : l'onglet ne le remplace pas.</t>
+          <t>Le dépôt choisi lui est IMPOSÉ et la recherche est relancée : les quatre onglets parlent du même dépôt. Le choix reste modifiable dans l'onglet.</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -2307,67 +2307,67 @@
       <c r="F68" s="15" t="n"/>
       <c r="G68" s="16" t="n"/>
     </row>
-    <row r="69" ht="19" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Menu d'origine conservé</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir le menu « Point Caisse Dépôt » habituel.</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Il fonctionne exactement comme avant : l'onglet ne le remplace pas.</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>d1ec13e</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>H. AFFICHAGE — « LA PAGE S'EST RÉDUITE, LA VUE EST TRONQUÉE »</t>
         </is>
       </c>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
-      <c r="E69" s="8" t="n"/>
-      <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="n"/>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="8" t="n"/>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Redimensionnement</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>Ouvrir n'importe quel écran, puis agrandir et réduire plusieurs fois la fenêtre du navigateur.</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>Le contenu suit la fenêtre à chaque fois. Aucune bande blanche à droite, aucun écran figé à son ancienne largeur.</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>7a2b800</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="n"/>
-      <c r="G70" s="16" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>Après un geste ordinaire</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Agrandir la fenêtre, puis lancer une recherche ou ajouter un produit à une vente.</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>L'écran ne se retracte pas : il garde la largeur de la fenêtre.</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -2378,25 +2378,25 @@
       <c r="F71" s="15" t="n"/>
       <c r="G71" s="16" t="n"/>
     </row>
-    <row r="72" ht="54" customHeight="1">
+    <row r="72" ht="30" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>Robustesse</t>
+          <t>Après un geste ordinaire</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>Enchaîner : ouvrir plusieurs écrans, redimensionner entre chacun, revenir en arrière.</t>
+          <t>Agrandir la fenêtre, puis lancer une recherche ou ajouter un produit à une vente.</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>Aucun écran ne reste bloqué à une ancienne taille. Si un incident d'affichage survient malgré tout, il est journalisé dans le Centre de Support (écran Diagnostic / Historique) — ce n'est plus silencieux.</t>
+          <t>L'écran ne se retracte pas : il garde la largeur de la fenêtre.</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -2407,154 +2407,154 @@
       <c r="F72" s="15" t="n"/>
       <c r="G72" s="16" t="n"/>
     </row>
-    <row r="73" ht="30" customHeight="1">
+    <row r="73" ht="54" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Écran de vente en onglet</t>
+          <t>Robustesse</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir l'onglet Saisir vente dépôt sur un poste en 1366 px de large.</t>
+          <t>Enchaîner : ouvrir plusieurs écrans, redimensionner entre chacun, revenir en arrière.</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>L'écran de vente est entièrement visible, colonne RÈGLEMENT comprise. Aucun défilement horizontal de la page.</t>
+          <t>Aucun écran ne reste bloqué à une ancienne taille. Si un incident d'affichage survient malgré tout, il est journalisé dans le Centre de Support (écran Diagnostic / Historique) — ce n'est plus silencieux.</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>647702e</t>
+          <t>7a2b800</t>
         </is>
       </c>
       <c r="F73" s="15" t="n"/>
       <c r="G73" s="16" t="n"/>
     </row>
-    <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Écran de vente en onglet</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir l'onglet Saisir vente dépôt sur un poste en 1366 px de large.</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>L'écran de vente est entièrement visible, colonne RÈGLEMENT comprise. Aucun défilement horizontal de la page.</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>647702e</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="n"/>
+      <c r="G74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>I. ANALYSE POSOLOGIE (POSOS)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="n"/>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="n"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>Ouvrir le menu « Analyse Posologie ».</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Le menu existe, son libellé est court et tient dans la navigation.</t>
         </is>
       </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="E76" s="14" t="inlineStr">
         <is>
           <t>5c13ca8</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="n"/>
-      <c r="G75" s="16" t="n"/>
-    </row>
-    <row r="76" ht="42" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>Non configuré</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>Ouvrir l'écran AVANT d'avoir renseigné posos.properties.</t>
-        </is>
-      </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>Un bandeau annonce que la passerelle n'est pas configurée et AFFICHE LE CHEMIN EXACT du fichier attendu, en disant s'il est présent.</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
-        <is>
-          <t>573c7ee</t>
         </is>
       </c>
       <c r="F76" s="15" t="n"/>
       <c r="G76" s="16" t="n"/>
     </row>
-    <row r="77" ht="54" customHeight="1">
+    <row r="77" ht="42" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Aucun secret exposé</t>
+          <t>Non configuré</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>Renseigner posos.properties, puis appeler api/v1/posos/status depuis le navigateur.</t>
+          <t>Ouvrir l'écran AVANT d'avoir renseigné posos.properties.</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>La réponse ne rend que l'adresse, les chemins, l'identifiant MASQUÉ et des booléens. Ni le secret, ni l'identifiant en clair, ni le jeton n'apparaissent — ni ici, ni dans les journaux.</t>
+          <t>Un bandeau annonce que la passerelle n'est pas configurée et AFFICHE LE CHEMIN EXACT du fichier attendu, en disant s'il est présent.</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>60696a4</t>
+          <t>573c7ee</t>
         </is>
       </c>
       <c r="F77" s="15" t="n"/>
       <c r="G77" s="16" t="n"/>
     </row>
-    <row r="78" ht="42" customHeight="1">
+    <row r="78" ht="54" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>Analyse d'une ordonnance</t>
+          <t>Aucun secret exposé</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>Depuis une vente, demander l'analyse des produits de l'ordonnance.</t>
+          <t>Renseigner posos.properties, puis appeler api/v1/posos/status depuis le navigateur.</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>Les produits sont envoyés PAR LEUR NOM. Les alertes reviennent classées, et une alerte de gravité inconnue est traitée comme MAJEURE — jamais minimisée.</t>
+          <t>La réponse ne rend que l'adresse, les chemins, l'identifiant MASQUÉ et des booléens. Ni le secret, ni l'identifiant en clair, ni le jeton n'apparaissent — ni ici, ni dans les journaux.</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -2565,25 +2565,25 @@
       <c r="F78" s="15" t="n"/>
       <c r="G78" s="16" t="n"/>
     </row>
-    <row r="79" ht="30" customHeight="1">
+    <row r="79" ht="42" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>I5</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Changement d'identifiants</t>
+          <t>Analyse d'une ordonnance</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>Modifier le secret dans posos.properties, puis relancer une analyse.</t>
+          <t>Depuis une vente, demander l'analyse des produits de l'ordonnance.</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>Le jeton mémorisé est abandonné et un nouveau est demandé : on ne continue pas avec d'anciens identifiants.</t>
+          <t>Les produits sont envoyés PAR LEUR NOM. Les alertes reviennent classées, et une alerte de gravité inconnue est traitée comme MAJEURE — jamais minimisée.</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -2594,96 +2594,96 @@
       <c r="F79" s="15" t="n"/>
       <c r="G79" s="16" t="n"/>
     </row>
-    <row r="80" ht="19" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Changement d'identifiants</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Modifier le secret dans posos.properties, puis relancer une analyse.</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Le jeton mémorisé est abandonné et un nouveau est demandé : on ne continue pas avec d'anciens identifiants.</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>60696a4</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="n"/>
+      <c r="G80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="19" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>J. CLIENTS — CRÉATION STANDARD ET IMPORT</t>
         </is>
       </c>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Création allégée</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>Écran des clients : cliquer « Creer client standard ».</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="inlineStr">
-        <is>
-          <t>La fenêtre ne demande que le nom, les prénoms et le téléphone. Le formulaire complet reste disponible par le bouton « Creer ».</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
-        <is>
-          <t>96e4e66</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="n"/>
-      <c r="G81" s="16" t="n"/>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>Entrée enchaîne les champs</t>
+          <t>Création allégée</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>Curseur dans Nom : taper le nom, Entrée ; taper les prénoms, Entrée ; taper le numéro, Entrée.</t>
+          <t>Écran des clients : cliquer « Creer client standard ».</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Entrée passe au champ SUIVANT (nom → prénoms → numéro → bouton Enregistrer), et n'enregistre pas depuis le premier champ.</t>
+          <t>La fenêtre ne demande que le nom, les prénoms et le téléphone. Le formulaire complet reste disponible par le bouton « Creer ».</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>8acf705</t>
+          <t>96e4e66</t>
         </is>
       </c>
       <c r="F82" s="15" t="n"/>
       <c r="G82" s="16" t="n"/>
     </row>
-    <row r="83" ht="30" customHeight="1">
+    <row r="83" ht="42" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Le bouton est une étape</t>
+          <t>Entrée enchaîne les champs</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>Après la troisième frappe d'Entrée, regarder l'écran sans rien taper.</t>
+          <t>Curseur dans Nom : taper le nom, Entrée ; taper les prénoms, Entrée ; taper le numéro, Entrée.</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Le focus est sur Enregistrer, RIEN n'est encore enregistré. Une seconde frappe d'Entrée (ou Espace) enregistre.</t>
+          <t>Entrée passe au champ SUIVANT (nom → prénoms → numéro → bouton Enregistrer), et n'enregistre pas depuis le premier champ.</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
@@ -2694,25 +2694,25 @@
       <c r="F83" s="15" t="n"/>
       <c r="G83" s="16" t="n"/>
     </row>
-    <row r="84" ht="42" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>Animation de la vente</t>
+          <t>Le bouton est une étape</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>Observer le champ actif pendant la saisie, puis le bouton quand le focus l'atteint.</t>
+          <t>Après la troisième frappe d'Entrée, regarder l'écran sans rien taper.</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>Le champ actif bat comme dans l'écran de vente ; le bouton prend le même battement. Revenir dans un champ éteint le battement du bouton.</t>
+          <t>Le focus est sur Enregistrer, RIEN n'est encore enregistré. Une seconde frappe d'Entrée (ou Espace) enregistre.</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -2726,27 +2726,27 @@
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Numéro unique</t>
+          <t>Animation de la vente</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>Créer un second client standard avec un numéro déjà utilisé, y compris écrit autrement (+225 07-08-...).</t>
+          <t>Observer le champ actif pendant la saisie, puis le bouton quand le focus l'atteint.</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Refusé, en NOMMANT le client qui détient le numéro, pour qu'on retrouve sa fiche au lieu d'en créer une seconde. Le numéro est enregistré normalisé, sans séparateurs.</t>
+          <t>Le champ actif bat comme dans l'écran de vente ; le bouton prend le même battement. Revenir dans un champ éteint le battement du bouton.</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>96e4e66</t>
+          <t>8acf705</t>
         </is>
       </c>
       <c r="F85" s="15" t="n"/>
@@ -2755,22 +2755,22 @@
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>Non-régression assurance</t>
+          <t>Numéro unique</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>Créer deux clients NON standards (assurance) avec le même numéro.</t>
+          <t>Créer un second client standard avec un numéro déjà utilisé, y compris écrit autrement (+225 07-08-...).</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>Accepté : l'unicité ne porte que sur les clients standards. Deux assurés d'une même famille peuvent partager un numéro.</t>
+          <t>Refusé, en NOMMANT le client qui détient le numéro, pour qu'on retrouve sa fiche au lieu d'en créer une seconde. Le numéro est enregistré normalisé, sans séparateurs.</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -2781,30 +2781,30 @@
       <c r="F86" s="15" t="n"/>
       <c r="G86" s="16" t="n"/>
     </row>
-    <row r="87" ht="30" customHeight="1">
+    <row r="87" ht="42" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Import sous privilège</t>
+          <t>Non-régression assurance</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>Avec un profil SANS P_IMPORT_CLIENTS, ouvrir l'écran des clients.</t>
+          <t>Créer deux clients NON standards (assurance) avec le même numéro.</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Les DEUX boutons d'import (« Importer » et « Importer (colonnes au choix) ») sont cachés.</t>
+          <t>Accepté : l'unicité ne porte que sur les clients standards. Deux assurés d'une même famille peuvent partager un numéro.</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>7a2b800</t>
+          <t>96e4e66</t>
         </is>
       </c>
       <c r="F87" s="15" t="n"/>
@@ -2813,22 +2813,22 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>Import : contrôle serveur</t>
+          <t>Import sous privilège</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>Sans le privilège, appeler directement les services d'import.</t>
+          <t>Avec un profil SANS P_IMPORT_CLIENTS, ouvrir l'écran des clients.</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>Les deux services refusent : « Votre profil ne permet pas d'importer des clients. »</t>
+          <t>Les DEUX boutons d'import (« Importer » et « Importer (colonnes au choix) ») sont cachés.</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -2839,54 +2839,54 @@
       <c r="F88" s="15" t="n"/>
       <c r="G88" s="16" t="n"/>
     </row>
-    <row r="89" ht="66" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>J9</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Import colonnes au choix</t>
+          <t>Import : contrôle serveur</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>Avec le privilège : choisir un fichier, lire ses colonnes, désigner nom / prénoms / numéro, contrôler, importer.</t>
+          <t>Sans le privilège, appeler directement les services d'import.</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Le séparateur est détecté et annoncé ; les colonnes sont pré-désignées d'après les titres même dans un ordre inattendu ; le contrôle n'écrit RIEN et rend un rapport ligne à ligne avec les motifs de rejet ; l'import n'écrit que les lignes retenues.</t>
+          <t>Les deux services refusent : « Votre profil ne permet pas d'importer des clients. »</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>1856144</t>
+          <t>7a2b800</t>
         </is>
       </c>
       <c r="F89" s="15" t="n"/>
       <c r="G89" s="16" t="n"/>
     </row>
-    <row r="90" ht="30" customHeight="1">
+    <row r="90" ht="66" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>J10</t>
+          <t>J9</t>
         </is>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Import : pas de double</t>
+          <t>Import colonnes au choix</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>Relancer le même fichier une seconde fois.</t>
+          <t>Avec le privilège : choisir un fichier, lire ses colonnes, désigner nom / prénoms / numéro, contrôler, importer.</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>Aucune ligne n'est retenue : les numéros sont déjà attribués. Le bouton d'import se désactive après écriture.</t>
+          <t>Le séparateur est détecté et annoncé ; les colonnes sont pré-désignées d'après les titres même dans un ordre inattendu ; le contrôle n'écrit RIEN et rend un rapport ligne à ligne avec les motifs de rejet ; l'import n'écrit que les lignes retenues.</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -2897,67 +2897,67 @@
       <c r="F90" s="15" t="n"/>
       <c r="G90" s="16" t="n"/>
     </row>
-    <row r="91" ht="19" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Import : pas de double</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Relancer le même fichier une seconde fois.</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Aucune ligne n'est retenue : les numéros sont déjà attribués. Le bouton d'import se désactive après écriture.</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>1856144</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="n"/>
+      <c r="G91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="19" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>K. STOCK — RAYON, RÉSERVE ET TOTAL</t>
         </is>
       </c>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="n"/>
-    </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>Trois quantités</t>
         </is>
       </c>
-      <c r="C92" s="13" t="inlineStr">
+      <c r="C93" s="13" t="inlineStr">
         <is>
           <t>Ouvrir « Etat de stock », puis « Comparaison stock article ».</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
         <is>
           <t>Les deux écrans affichent le stock RAYON, la RÉSERVE et le TOTAL. Le total est calculé (rayon + réserve) : il ne peut pas se désynchroniser.</t>
-        </is>
-      </c>
-      <c r="E92" s="14" t="inlineStr">
-        <is>
-          <t>5006217</t>
-        </is>
-      </c>
-      <c r="F92" s="15" t="n"/>
-      <c r="G92" s="16" t="n"/>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>K2</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Masquage des quantités</t>
-        </is>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>Positionner le paramètre AFFICHER_STOCK à « masqué », puis rouvrir les écrans et exporter.</t>
-        </is>
-      </c>
-      <c r="D93" s="13" t="inlineStr">
-        <is>
-          <t>Les trois colonnes sont vides à l'écran ET dans l'export : l'export ne contourne pas le masquage.</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
@@ -2968,30 +2968,30 @@
       <c r="F93" s="15" t="n"/>
       <c r="G93" s="16" t="n"/>
     </row>
-    <row r="94" ht="54" customHeight="1">
+    <row r="94" ht="30" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Édition avec réserve</t>
+          <t>Masquage des quantités</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Imprimer réserve » dans chacun des deux écrans.</t>
+          <t>Positionner le paramètre AFFICHER_STOCK à « masqué », puis rouvrir les écrans et exporter.</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>Le PDF s'ouvre dans un onglet, porte les colonnes Rayon / Réserve / Total et leurs valorisations, et rappelle les critères. Les éditions historiques des deux écrans sont conservées à côté.</t>
+          <t>Les trois colonnes sont vides à l'écran ET dans l'export : l'export ne contourne pas le masquage.</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>1ed67f3</t>
+          <t>5006217</t>
         </is>
       </c>
       <c r="F94" s="15" t="n"/>
@@ -3000,51 +3000,51 @@
     <row r="95" ht="54" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Tri par emplacement</t>
+          <t>Édition avec réserve</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>Éditer sans filtre (tout le catalogue) et parcourir le document.</t>
+          <t>Cliquer « Imprimer réserve » dans chacun des deux écrans.</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Les produits sont triés PAR EMPLACEMENT, puis par désignation. Les articles sans emplacement passent en DERNIER. Mesure au banc : 6 753 articles, rayons croissants du premier au dernier.</t>
+          <t>Le PDF s'ouvre dans un onglet, porte les colonnes Rayon / Réserve / Total et leurs valorisations, et rappelle les critères. Les éditions historiques des deux écrans sont conservées à côté.</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>30a8957</t>
+          <t>1ed67f3</t>
         </is>
       </c>
       <c r="F95" s="15" t="n"/>
       <c r="G95" s="16" t="n"/>
     </row>
-    <row r="96" ht="42" customHeight="1">
+    <row r="96" ht="54" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Tri par emplacement</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>Aller à la dernière page du même document.</t>
+          <t>Éditer sans filtre (tout le catalogue) et parcourir le document.</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>« Page X / Y » sur chaque page (mesure : 158 pages, dernière page « Page 158 / 158 »), avec la date, l'opérateur et le rappel du tri.</t>
+          <t>Les produits sont triés PAR EMPLACEMENT, puis par désignation. Les articles sans emplacement passent en DERNIER. Mesure au banc : 6 753 articles, rayons croissants du premier au dernier.</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -3055,96 +3055,96 @@
       <c r="F96" s="15" t="n"/>
       <c r="G96" s="16" t="n"/>
     </row>
-    <row r="97" ht="54" customHeight="1">
+    <row r="97" ht="42" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Plus de blocage</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>Lancer l'édition « Imprimer réserve » de la comparaison d'articles sur tout le catalogue et chronométrer.</t>
+          <t>Aller à la dernière page du même document.</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Le document sort (mesure : 1,7 s pour l'état de stock, 15,7 s pour la comparaison). Le blocage de 327 s signalé n'existe plus. Note : les 15,7 s restantes viennent de la requête historique de cet écran — chantier à décider.</t>
+          <t>« Page X / Y » sur chaque page (mesure : 158 pages, dernière page « Page 158 / 158 »), avec la date, l'opérateur et le rappel du tri.</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>bc094f1</t>
+          <t>30a8957</t>
         </is>
       </c>
       <c r="F97" s="15" t="n"/>
       <c r="G97" s="16" t="n"/>
     </row>
-    <row r="98" ht="19" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
+    <row r="98" ht="54" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>Plus de blocage</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>Lancer l'édition « Imprimer réserve » de la comparaison d'articles sur tout le catalogue et chronométrer.</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>Le document sort (mesure : 1,7 s pour l'état de stock, 15,7 s pour la comparaison). Le blocage de 327 s signalé n'existe plus. Note : les 15,7 s restantes viennent de la requête historique de cet écran — chantier à décider.</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>bc094f1</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="n"/>
+      <c r="G98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="19" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>L. SUGGESTIONS DE RÉAPPRO — ÉCLATER</t>
         </is>
       </c>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="n"/>
-    </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Le bouton existe</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>Ouvrir « Suggestion de reappro » et regarder la barre d'outils.</t>
-        </is>
-      </c>
-      <c r="D99" s="13" t="inlineStr">
-        <is>
-          <t>Un bouton « ÉCLATER » figure à côté de FUSIONNER.</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
-        <is>
-          <t>b27aa4c</t>
-        </is>
-      </c>
-      <c r="F99" s="15" t="n"/>
-      <c r="G99" s="16" t="n"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Sans sélection</t>
+          <t>Le bouton existe</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>Cliquer ÉCLATER sans rien cocher.</t>
+          <t>Ouvrir « Suggestion de reappro » et regarder la barre d'outils.</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>Il demande de cocher la suggestion à éclater, et ne fait rien.</t>
+          <t>Un bouton « ÉCLATER » figure à côté de FUSIONNER.</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
@@ -3158,22 +3158,22 @@
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Une seule à la fois</t>
+          <t>Sans sélection</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>Cocher deux suggestions, puis cliquer ÉCLATER.</t>
+          <t>Cliquer ÉCLATER sans rien cocher.</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Refusé : l'éclatement porte sur une suggestion à la fois.</t>
+          <t>Il demande de cocher la suggestion à éclater, et ne fait rien.</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
@@ -3184,25 +3184,25 @@
       <c r="F101" s="15" t="n"/>
       <c r="G101" s="16" t="n"/>
     </row>
-    <row r="102" ht="42" customHeight="1">
+    <row r="102" ht="30" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Éclatement</t>
+          <t>Une seule à la fois</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>Cocher une suggestion, cliquer ÉCLATER, saisir 3.</t>
+          <t>Cocher deux suggestions, puis cliquer ÉCLATER.</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>Trois suggestions sont obtenues, nommées dans le message avec leur nombre de lignes. Une suggestion de 1 500 lignes donne 3 × 500.</t>
+          <t>Refusé : l'éclatement porte sur une suggestion à la fois.</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -3216,22 +3216,22 @@
     <row r="103" ht="42" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Aucune ligne perdue</t>
+          <t>Éclatement</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>Noter le nombre de lignes avant, puis additionner les lignes des morceaux obtenus.</t>
+          <t>Cocher une suggestion, cliquer ÉCLATER, saisir 3.</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>La somme est EXACTEMENT le nombre de départ : aucune ligne perdue, aucune dupliquée. Le reste de la division va aux premiers morceaux (1 501 en 3 → 501 / 500 / 500).</t>
+          <t>Trois suggestions sont obtenues, nommées dans le message avec leur nombre de lignes. Une suggestion de 1 500 lignes donne 3 × 500.</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
@@ -3245,22 +3245,22 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>Identité conservée</t>
+          <t>Aucune ligne perdue</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>Retrouver les morceaux dans la liste.</t>
+          <t>Noter le nombre de lignes avant, puis additionner les lignes des morceaux obtenus.</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>La suggestion de départ GARDE sa référence et devient le premier morceau. Tous les morceaux sont des suggestions MANUELLES, chez le même grossiste que l'originale.</t>
+          <t>La somme est EXACTEMENT le nombre de départ : aucune ligne perdue, aucune dupliquée. Le reste de la division va aux premiers morceaux (1 501 en 3 → 501 / 500 / 500).</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
@@ -3274,22 +3274,22 @@
     <row r="105" ht="42" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Refus explicites</t>
+          <t>Identité conservée</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>Essayer : éclater en 1 ; éclater en plus de morceaux qu'il y a de lignes ; éclater une suggestion DÉJÀ COMMANDÉE ; éclater une suggestion vide.</t>
+          <t>Retrouver les morceaux dans la liste.</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Chaque cas est refusé avec son motif — le nombre de lignes disponibles est rappelé, et la suggestion déjà commandée est nommée. Elle ressort intacte.</t>
+          <t>La suggestion de départ GARDE sa référence et devient le premier morceau. Tous les morceaux sont des suggestions MANUELLES, chez le même grossiste que l'originale.</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -3300,25 +3300,25 @@
       <c r="F105" s="15" t="n"/>
       <c r="G105" s="16" t="n"/>
     </row>
-    <row r="106" ht="26" customHeight="1">
+    <row r="106" ht="42" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>Non-régression FUSIONNER</t>
+          <t>Refus explicites</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>Fusionner deux suggestions du même grossiste.</t>
+          <t>Essayer : éclater en 1 ; éclater en plus de morceaux qu'il y a de lignes ; éclater une suggestion DÉJÀ COMMANDÉE ; éclater une suggestion vide.</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>La fusion fonctionne comme avant.</t>
+          <t>Chaque cas est refusé avec son motif — le nombre de lignes disponibles est rappelé, et la suggestion déjà commandée est nommée. Elle ressort intacte.</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -3329,67 +3329,67 @@
       <c r="F106" s="15" t="n"/>
       <c r="G106" s="16" t="n"/>
     </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
+    <row r="107" ht="26" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Non-régression FUSIONNER</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Fusionner deux suggestions du même grossiste.</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>La fusion fonctionne comme avant.</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>b27aa4c</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="n"/>
+      <c r="G107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="19" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>M. TICKET Z ET BALANCE</t>
         </is>
       </c>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="8" t="n"/>
+      <c r="G108" s="8" t="n"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B108" s="12" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>Ligne « dont vente dépôt »</t>
         </is>
       </c>
-      <c r="C108" s="13" t="inlineStr">
+      <c r="C109" s="13" t="inlineStr">
         <is>
           <t>Après une vente en dépôt, afficher le ticket Z de l'opérateur.</t>
         </is>
       </c>
-      <c r="D108" s="13" t="inlineStr">
+      <c r="D109" s="13" t="inlineStr">
         <is>
           <t>Une ligne « dont vente dépôt &lt;nom du dépôt&gt; » apparaît, avec son montant.</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="inlineStr">
-        <is>
-          <t>52da772</t>
-        </is>
-      </c>
-      <c r="F108" s="15" t="n"/>
-      <c r="G108" s="16" t="n"/>
-    </row>
-    <row r="109" ht="42" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>Totaux inchangés</t>
-        </is>
-      </c>
-      <c r="C109" s="13" t="inlineStr">
-        <is>
-          <t>Comparer le total espèces du ticket Z à la somme des ventes du jour, dépôt comprise.</t>
-        </is>
-      </c>
-      <c r="D109" s="13" t="inlineStr">
-        <is>
-          <t>Le total est INCHANGÉ : la ventilation ne s'ajoute pas au total, elle en fait partie. L'argent du dépôt est bien dans ce tiroir.</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -3403,51 +3403,51 @@
     <row r="110" ht="42" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>Temps de réponse</t>
+          <t>Totaux inchangés</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>Afficher le ticket Z sur une journée chargée et chronométrer.</t>
+          <t>Comparer le total espèces du ticket Z à la somme des ventes du jour, dépôt comprise.</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>Mesure A/B au banc sur 300 ventes : 3 693 ms avant, 1 489 ms après (1 118 ms à chaud). L'écart se creuse avec le nombre de ventes.</t>
+          <t>Le total est INCHANGÉ : la ventilation ne s'ajoute pas au total, elle en fait partie. L'argent du dépôt est bien dans ce tiroir.</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>9d214eb</t>
+          <t>52da772</t>
         </is>
       </c>
       <c r="F110" s="15" t="n"/>
       <c r="G110" s="16" t="n"/>
     </row>
-    <row r="111" ht="54" customHeight="1">
+    <row r="111" ht="42" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Balance sans règlement</t>
+          <t>Temps de réponse</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir la balance sur une période contenant une vente clôturée SANS ligne de règlement.</t>
+          <t>Afficher le ticket Z sur une journée chargée et chronométrer.</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>L'écran s'affiche normalement. La vente compte dans le chiffre d'affaires, mais dans aucun mode de règlement : le total des modes est alors inférieur au net, ce qui est l'information exacte. Avant, l'écran tombait.</t>
+          <t>Mesure A/B au banc sur 300 ventes : 3 693 ms avant, 1 489 ms après (1 118 ms à chaud). L'écart se creuse avec le nombre de ventes.</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
@@ -3458,96 +3458,96 @@
       <c r="F111" s="15" t="n"/>
       <c r="G111" s="16" t="n"/>
     </row>
-    <row r="112" ht="30" customHeight="1">
+    <row r="112" ht="54" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>Balance dépôt</t>
+          <t>Balance sans règlement</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir « Balance Depot » et lancer une recherche.</t>
+          <t>Ouvrir la balance sur une période contenant une vente clôturée SANS ligne de règlement.</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr">
         <is>
-          <t>L'écran fonctionne comme avant : les privilèges des onglets de l'écran des dépôts ne l'ont pas touché.</t>
+          <t>L'écran s'affiche normalement. La vente compte dans le chiffre d'affaires, mais dans aucun mode de règlement : le total des modes est alors inférieur au net, ce qui est l'information exacte. Avant, l'écran tombait.</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>d1ec13e</t>
+          <t>9d214eb</t>
         </is>
       </c>
       <c r="F112" s="15" t="n"/>
       <c r="G112" s="16" t="n"/>
     </row>
-    <row r="113" ht="19" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Balance dépôt</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir « Balance Depot » et lancer une recherche.</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>L'écran fonctionne comme avant : les privilèges des onglets de l'écran des dépôts ne l'ont pas touché.</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>d1ec13e</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="n"/>
+      <c r="G113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="19" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>N. AUTRES POINTS DE L'ÉVOLUTION 5</t>
         </is>
       </c>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="n"/>
-    </row>
-    <row r="114" ht="54" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="n"/>
+    </row>
+    <row r="115" ht="54" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>Valorisation archivée</t>
         </is>
       </c>
-      <c r="C114" s="13" t="inlineStr">
+      <c r="C115" s="13" t="inlineStr">
         <is>
           <t>Vérifier le sous-dossier « valorisations » de la racine de stockage après le 27 du mois.</t>
         </is>
       </c>
-      <c r="D114" s="13" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
         <is>
           <t>Un PDF valorisation_&lt;officine&gt;_du_&lt;AAAA-MM-JJ&gt;.pdf y a été produit tout seul à 01:20. Le critère (EMPLACEMENT ou FAMILLE) suit le paramètre KEY_VALORISATION_PDF_CRITERE, et la purge garde 12 mois par défaut.</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>a245ffe</t>
-        </is>
-      </c>
-      <c r="F114" s="15" t="n"/>
-      <c r="G114" s="16" t="n"/>
-    </row>
-    <row r="115" ht="30" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>N2</t>
-        </is>
-      </c>
-      <c r="B115" s="12" t="inlineStr">
-        <is>
-          <t>Valorisation : écran inchangé</t>
-        </is>
-      </c>
-      <c r="C115" s="13" t="inlineStr">
-        <is>
-          <t>Produire la valorisation depuis l'écran.</t>
-        </is>
-      </c>
-      <c r="D115" s="13" t="inlineStr">
-        <is>
-          <t>Le document est exactement le même qu'avant : l'archivage est un second appel en lecture seule.</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
@@ -3558,30 +3558,30 @@
       <c r="F115" s="15" t="n"/>
       <c r="G115" s="16" t="n"/>
     </row>
-    <row r="116" ht="54" customHeight="1">
+    <row r="116" ht="30" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Ventes supprimées</t>
+          <t>Valorisation : écran inchangé</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir l'écran des suppressions de vente.</t>
+          <t>Produire la valorisation depuis l'écran.</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>Une colonne « Vente ouverte par » figure à côté de « Supprimé par », et dans l'export Excel. Pour une suppression automatique de nuit, « Supprimé par » vaut Système et « Vente ouverte par » nomme l'opérateur.</t>
+          <t>Le document est exactement le même qu'avant : l'archivage est un second appel en lecture seule.</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>2e61fed</t>
+          <t>a245ffe</t>
         </is>
       </c>
       <c r="F116" s="15" t="n"/>
@@ -3590,80 +3590,80 @@
     <row r="117" ht="54" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Règlement carnet dépôt</t>
+          <t>Ventes supprimées</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>Saisir un règlement de carnet dépôt en choisissant une date ANCIENNE (plusieurs semaines).</t>
+          <t>Ouvrir l'écran des suppressions de vente.</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Deux colonnes distinctes : « Date de reglement » (la date choisie) et « Saisi le » (l'horodatage réel de la saisie). Le dossier, le mouvement de caisse et le ticket restent datés de la date choisie.</t>
+          <t>Une colonne « Vente ouverte par » figure à côté de « Supprimé par », et dans l'export Excel. Pour une suppression automatique de nuit, « Supprimé par » vaut Système et « Vente ouverte par » nomme l'opérateur.</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>75ff1d4</t>
+          <t>2e61fed</t>
         </is>
       </c>
       <c r="F117" s="15" t="n"/>
       <c r="G117" s="16" t="n"/>
     </row>
-    <row r="118" ht="42" customHeight="1">
+    <row r="118" ht="54" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Articles mouvementés</t>
+          <t>Règlement carnet dépôt</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>Ouvrir « articles mouvementés » et utiliser les trois filtres : mode de mouvement, emplacement, famille.</t>
+          <t>Saisir un règlement de carnet dépôt en choisissant une date ANCIENNE (plusieurs semaines).</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>Une seule ligne par article, même s'il a été vendu puis réapprovisionné ; la colonne « Type(s) de mouvement » concatène les modes. Réinitialiser remet tout à « Tous ».</t>
+          <t>Deux colonnes distinctes : « Date de reglement » (la date choisie) et « Saisi le » (l'horodatage réel de la saisie). Le dossier, le mouvement de caisse et le ticket restent datés de la date choisie.</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>59e700f</t>
+          <t>75ff1d4</t>
         </is>
       </c>
       <c r="F118" s="15" t="n"/>
       <c r="G118" s="16" t="n"/>
     </row>
-    <row r="119" ht="54" customHeight="1">
+    <row r="119" ht="42" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Inventaire sur toute la liste</t>
+          <t>Articles mouvementés</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Creer inventaire (toute la liste) » après avoir posé des filtres.</t>
+          <t>Ouvrir « articles mouvementés » et utiliser les trois filtres : mode de mouvement, emplacement, famille.</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>L'inventaire reprend TOUS les articles correspondant aux critères, sans cocher page par page, et son libellé rappelle le mode retenu. Le bouton par sélection est conservé.</t>
+          <t>Une seule ligne par article, même s'il a été vendu puis réapprovisionné ; la colonne « Type(s) de mouvement » concatène les modes. Réinitialiser remet tout à « Tous ».</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -3674,25 +3674,25 @@
       <c r="F119" s="15" t="n"/>
       <c r="G119" s="16" t="n"/>
     </row>
-    <row r="120" ht="42" customHeight="1">
+    <row r="120" ht="54" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>Export articles mouvementés</t>
+          <t>Inventaire sur toute la liste</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>Cliquer « Exporter Excel ».</t>
+          <t>Cliquer « Creer inventaire (toute la liste) » après avoir posé des filtres.</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>L'export répond (il était présenté mais non câblé), emporte les critères de l'écran et porte les trois nouvelles colonnes.</t>
+          <t>L'inventaire reprend TOUS les articles correspondant aux critères, sans cocher page par page, et son libellé rappelle le mode retenu. Le bouton par sélection est conservé.</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -3703,80 +3703,340 @@
       <c r="F120" s="15" t="n"/>
       <c r="G120" s="16" t="n"/>
     </row>
-    <row r="121" ht="30" customHeight="1">
+    <row r="121" ht="42" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>N8</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Rattrapage clôtures inventaire</t>
+          <t>Export articles mouvementés</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>Lancer le rattrapage des clôtures d'inventaire.</t>
+          <t>Cliquer « Exporter Excel ».</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Le traitement fonctionne et son test automatisé est de nouveau en place.</t>
+          <t>L'export répond (il était présenté mais non câblé), emporte les critères de l'écran et porte les trois nouvelles colonnes.</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>c622289</t>
+          <t>59e700f</t>
         </is>
       </c>
       <c r="F121" s="15" t="n"/>
       <c r="G121" s="16" t="n"/>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" s="17" t="inlineStr">
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>Rattrapage clôtures inventaire</t>
+        </is>
+      </c>
+      <c r="C122" s="13" t="inlineStr">
+        <is>
+          <t>Lancer le rattrapage des clôtures d'inventaire.</t>
+        </is>
+      </c>
+      <c r="D122" s="13" t="inlineStr">
+        <is>
+          <t>Le traitement fonctionne et son test automatisé est de nouveau en place.</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>c622289</t>
+        </is>
+      </c>
+      <c r="F122" s="15" t="n"/>
+      <c r="G122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="19" customHeight="1">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>O. GESTION DES SURSTOCKS</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="n"/>
+      <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="8" t="n"/>
+    </row>
+    <row r="124" ht="54" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>Somme des mois = quantité vendue</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir « Gestion des surstocks », rechercher avec 3 mois d'historique, relever une ligne, puis ouvrir la fiche article du même produit.</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>La quantité vendue de la période est EXACTEMENT la somme des trois derniers mois complets lus sur la fiche article (l'écart de 34 contre 35 signalé le 18/09). La période est calendaire : ni mois tronqué, ni mois en cours.</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F124" s="15" t="n"/>
+      <c r="G124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Les quatre mois rappelés</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="inlineStr">
+        <is>
+          <t>Regarder les en-têtes de colonnes et le rappel de période.</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>Le mois en cours et les trois précédents sont NOMMÉS (« Septembre (en cours) / Août / Juillet / Juin »), et un rappel dit sur quelle période porte le calcul.</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F125" s="15" t="n"/>
+      <c r="G125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="54" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Mois en cours exclu de la moyenne</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="inlineStr">
+        <is>
+          <t>Comparer la moyenne mensuelle à la somme des trois mois complets divisée par 3.</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>C'est la même valeur. Le mois en cours est affiché pour information mais n'entre NI dans la quantité vendue NI dans la moyenne : incomplet, il tirerait la moyenne vers le bas et gonflerait le surplus annoncé.</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F126" s="15" t="n"/>
+      <c r="G126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>O4</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Couleurs demandées</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="inlineStr">
+        <is>
+          <t>Regarder les colonnes Moy. mensuelle et Qté surplus.</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>La moyenne mensuelle est en BLEU, la quantité de surplus en VERT.</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F127" s="15" t="n"/>
+      <c r="G127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>O5</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>PDF et Excel cohérents</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="inlineStr">
+        <is>
+          <t>Imprimer puis exporter la même recherche.</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>Les quantités vendues et les moyennes du PDF et de l'Excel sont celles de l'écran, sur la même période.</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F128" s="15" t="n"/>
+      <c r="G128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="19" customHeight="1">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>P. MODES DE RÈGLEMENT — ICÔNES</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n"/>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="66" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>Tous les modes ont leur icône</t>
+        </is>
+      </c>
+      <c r="C130" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir une vente et déplier la liste des modes de paiement.</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>Les treize modes portent une icône, à la même taille et dans le même style : les cinq existantes (Wave, Orange, MTN, Moov, Djamo) et les huit ajoutées (espèces, carte bancaire, chèques, virement, différé, devise, Celpaid, TrésorPay).</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F130" s="15" t="n"/>
+      <c r="G130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="54" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Écran de vente inchangé</t>
+        </is>
+      </c>
+      <c r="C131" s="13" t="inlineStr">
+        <is>
+          <t>Enchaîner une vente complète avec règlement.</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>Rien d'autre n'a changé dans l'écran de vente : seules des images ont été ajoutées là où le code les cherchait déjà. Un mode sans image resterait affiché, simplement sans icône.</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>893f936</t>
+        </is>
+      </c>
+      <c r="F131" s="15" t="n"/>
+      <c r="G131" s="16" t="n"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="17" t="inlineStr">
         <is>
           <t>Vérifications automatisées existantes pour cette branche — suite unitaire : 901 cas. Bout en bout (src/test/e2e/retours) : test-depot-onglets 57, test-depot-extension-stock 55, test-vente-en-depot 31, test-posos 32, test-client-standard 32, test-import-clients 32, test-stock-reserve-colonnes 39, test-vente-contexte-depot 26, test-ca-depot 20, test-eclater-suggestion 19, test-redimensionnement 14, et les suites des points 2, 5, 6 et 8. Ces tests ne remplacent pas la recette : ils protègent des régressions, la recette valide l'usage.</t>
         </is>
       </c>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="18" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-    </row>
-    <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="19" t="inlineStr">
+      <c r="B133" s="18" t="n"/>
+      <c r="C133" s="18" t="n"/>
+      <c r="D133" s="18" t="n"/>
+      <c r="E133" s="18" t="n"/>
+      <c r="F133" s="18" t="n"/>
+      <c r="G133" s="18" t="n"/>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="19" t="inlineStr">
         <is>
           <t>Recette prononcée le ......... / ......... / .........          Visa du pharmacien : ..............................................          Réserves : ..............................................................................</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A91:G91"/>
-    <mergeCell ref="A125:G125"/>
+  <mergeCells count="22">
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A114:G114"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A98:G98"/>
-    <mergeCell ref="A107:G107"/>
     <mergeCell ref="A123:G123"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A70:G70"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A133:G133"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="G3:G7"/>
     <mergeCell ref="A3:D7"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A129:G129"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F10:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Verdict" error="Verdict attendu : OK, KO ou N/A." prompt="OK, KO ou N/A" type="list">
+    <dataValidation sqref="F10:F131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Verdict" error="Verdict attendu : OK, KO ou N/A." prompt="OK, KO ou N/A" type="list">
       <formula1>"OK,KO,N/A"</formula1>
     </dataValidation>
   </dataValidations>
